--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\progect test\projects\QRweb\qrtest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A948A1D-29D7-4414-B363-16783DC5E93E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA5B162-6EF7-4682-BDB5-9F777F4D670A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,14 +66,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Item Name</t>
   </si>
   <si>
-    <t>site</t>
-  </si>
-  <si>
     <t>In custody</t>
   </si>
   <si>
@@ -83,20 +80,44 @@
     <t>QR</t>
   </si>
   <si>
-    <t>مركبة</t>
-  </si>
-  <si>
-    <t>نجران</t>
-  </si>
-  <si>
-    <t>محمد</t>
+    <t>mr</t>
+  </si>
+  <si>
+    <t>najran</t>
+  </si>
+  <si>
+    <t>karim</t>
+  </si>
+  <si>
+    <t>1254 a s d</t>
+  </si>
+  <si>
+    <t>S/N &amp; VIN</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>md-1235-tr</t>
+  </si>
+  <si>
+    <t>1451541 wrwr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,28 +133,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor theme="5" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -142,21 +158,112 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color theme="5"/>
+      </left>
       <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="5"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="5"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="5"/>
+      </left>
+      <right style="thin">
+        <color theme="5"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="5"/>
       </right>
       <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="5"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="5"/>
+      </right>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="5"/>
+      </left>
+      <right style="thin">
+        <color theme="5"/>
+      </right>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="5"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -165,76 +272,172 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="14">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="5"/>
+        </top>
+        <bottom style="thin">
+          <color theme="5"/>
+        </bottom>
+      </border>
+      <protection locked="1" hidden="1"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <top style="thin">
+          <color theme="5"/>
+        </top>
+        <bottom style="thin">
+          <color theme="5"/>
+        </bottom>
+      </border>
+      <protection locked="1" hidden="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -255,12 +458,333 @@
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="5"/>
-          <bgColor theme="5"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <top style="thin">
+          <color theme="5"/>
+        </top>
+        <bottom style="thin">
+          <color theme="5"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <top style="thin">
+          <color theme="5"/>
+        </top>
+        <bottom style="thin">
+          <color theme="5"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <top style="thin">
+          <color theme="5"/>
+        </top>
+        <bottom style="thin">
+          <color theme="5"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <top style="thin">
+          <color theme="5"/>
+        </top>
+        <bottom style="thin">
+          <color theme="5"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <top style="thin">
+          <color theme="5"/>
+        </top>
+        <bottom style="thin">
+          <color theme="5"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <top style="thin">
+          <color theme="5"/>
+        </top>
+        <bottom style="thin">
+          <color theme="5"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <top style="thin">
+          <color theme="5"/>
+        </top>
+        <bottom style="thin">
+          <color theme="5"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color theme="5"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color theme="5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <top style="thin">
+          <color theme="5"/>
+        </top>
+        <bottom style="thin">
+          <color theme="5"/>
+        </bottom>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -346,7 +870,7 @@
     <v>90</v>
     <v>3</v>
     <v>90</v>
-    <v>مركبة</v>
+    <v>mr</v>
   </rv>
   <rv s="1">
     <v>1</v>
@@ -382,20 +906,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{512F4FF4-D5FD-4E7A-BDB5-0B0E9B262E20}" name="الجدول1" displayName="الجدول1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" tableBorderDxfId="5">
-  <autoFilter ref="A1:E6" xr:uid="{512F4FF4-D5FD-4E7A-BDB5-0B0E9B262E20}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C8670145-6822-45A6-889B-EA283A9776A8}" name="Item Name" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{6A52CDE7-B98E-4177-AF8E-389A7D3DC2FD}" name="site" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{AC59CE46-3D0E-42F9-8953-9732107D9A69}" name="In custody" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{C1219AB5-703A-431B-8112-51DA90BC26B7}" name="Data" dataDxfId="0">
-      <calculatedColumnFormula>"Item"&amp;": "&amp;الجدول1[[#This Row],[Item Name]]&amp;","&amp;CHAR(10)&amp;"Site"&amp;": "&amp;الجدول1[[#This Row],[site]]&amp;","&amp;CHAR(10)&amp;"In custody"&amp;": "&amp;الجدول1[[#This Row],[In custody]]</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CA936EB9-FB8E-43D6-8D81-EF7951F4DB6A}" name="الجدول2" displayName="الجدول2" ref="A1:I6" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2" headerRowBorderDxfId="12" tableBorderDxfId="13" totalsRowBorderDxfId="11">
+  <autoFilter ref="A1:I6" xr:uid="{CA936EB9-FB8E-43D6-8D81-EF7951F4DB6A}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{77BF3241-7481-4B75-8137-4C0743DCDABB}" name="Code" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{A1250C95-FC8D-4D2B-9E99-8478CE745A50}" name="Item Name" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{3ECC0821-1386-40FF-B178-AB39963B1C9B}" name="Model" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{615DDC40-34ED-423F-8BDD-983C72C5CC67}" name="Number" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{F02390A6-67A3-4139-B908-949365150532}" name="S/N &amp; VIN" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{EECFC1EB-9F3E-421F-A890-C1F61168C131}" name="Site" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{1029194C-B747-4829-9A79-898711220C87}" name="In custody" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{FD8D86F0-0205-4E00-B44B-293DCDF7D446}" name="Data" dataDxfId="1">
+      <calculatedColumnFormula>"Code"&amp;":"&amp;الجدول2[[#This Row],[Code]]&amp;","&amp;CHAR(10)&amp;"Item"&amp;": "&amp;ورقة1!$B2&amp;","&amp;CHAR(10)&amp;"Model"&amp;":"&amp;الجدول2[[#This Row],[Model]]&amp;","&amp;CHAR(10)&amp;"Number"&amp;":"&amp;الجدول2[[#This Row],[Number]]&amp;","&amp;CHAR(10)&amp;"S/N &amp; VIN"&amp;":"&amp;الجدول2[[#This Row],[S/N &amp; VIN]]&amp;","&amp;CHAR(10)&amp;"Site"&amp;": "&amp;ورقة1!$F2&amp;","&amp;CHAR(10)&amp;"In custody"&amp;": "&amp;ورقة1!$G2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D9BEF5D3-7E3E-417E-869E-CD8F67975B21}" name="QR" dataDxfId="1">
-      <calculatedColumnFormula>_xlfn.IMAGE("https://quickchart.io/qr?text=" &amp; _xlfn.ENCODEURL(D2),الجدول1[[#This Row],[Item Name]],3,90,90)</calculatedColumnFormula>
+    <tableColumn id="9" xr3:uid="{706C5480-AA51-494F-891F-DFF741CC1C73}" name="QR" dataDxfId="0">
+      <calculatedColumnFormula>_xlfn.IMAGE("https://quickchart.io/qr?text=" &amp; _xlfn.ENCODEURL(H2),ورقة1!$B2,3,90,90)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -662,111 +1190,179 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" style="8" customWidth="1"/>
-    <col min="2" max="3" width="32.85546875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="55.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" style="6" customWidth="1"/>
+    <col min="2" max="5" width="30.7109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="26.7109375" style="14" customWidth="1"/>
+    <col min="7" max="7" width="26.85546875" style="14" customWidth="1"/>
+    <col min="8" max="8" width="38.28515625" style="15" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:9" s="10" customFormat="1" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="C2" s="8">
+        <v>2024</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="16" t="str">
+        <f>"Code"&amp;":"&amp;الجدول2[[#This Row],[Code]]&amp;","&amp;CHAR(10)&amp;"Item"&amp;": "&amp;ورقة1!$B2&amp;","&amp;CHAR(10)&amp;"Model"&amp;":"&amp;الجدول2[[#This Row],[Model]]&amp;","&amp;CHAR(10)&amp;"Number"&amp;":"&amp;الجدول2[[#This Row],[Number]]&amp;","&amp;CHAR(10)&amp;"S/N &amp; VIN"&amp;":"&amp;الجدول2[[#This Row],[S/N &amp; VIN]]&amp;","&amp;CHAR(10)&amp;"Site"&amp;": "&amp;ورقة1!$F2&amp;","&amp;CHAR(10)&amp;"In custody"&amp;": "&amp;ورقة1!$G2</f>
+        <v>Code:md-1235-tr,
+Item: mr,
+Model:2024,
+Number:1254 a s d,
+S/N &amp; VIN:1451541 wrwr,
+Site: najran,
+In custody: karim</v>
+      </c>
+      <c r="I2" s="17" t="e" vm="1">
+        <f>_xlfn.IMAGE("https://quickchart.io/qr?text=" &amp; _xlfn.ENCODEURL(H2),ورقة1!$B2,3,90,90)</f>
+        <v>#VALUE!</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" s="4" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="6" t="str">
-        <f>"Item"&amp;": "&amp;الجدول1[[#This Row],[Item Name]]&amp;","&amp;CHAR(10)&amp;"Site"&amp;": "&amp;الجدول1[[#This Row],[site]]&amp;","&amp;CHAR(10)&amp;"In custody"&amp;": "&amp;الجدول1[[#This Row],[In custody]]</f>
-        <v>Item: مركبة,
-Site: نجران,
-In custody: محمد</v>
-      </c>
-      <c r="E2" s="4" t="e" vm="1">
-        <f>_xlfn.IMAGE("https://quickchart.io/qr?text=" &amp; _xlfn.ENCODEURL(D2),الجدول1[[#This Row],[Item Name]],3,90,90)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="4" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="7" t="str">
-        <f>"Item"&amp;": "&amp;الجدول1[[#This Row],[Item Name]]&amp;","&amp;CHAR(10)&amp;"Site"&amp;": "&amp;الجدول1[[#This Row],[site]]&amp;","&amp;CHAR(10)&amp;"In custody"&amp;": "&amp;الجدول1[[#This Row],[In custody]]</f>
-        <v xml:space="preserve">Item: ,
+    <row r="3" spans="1:9" s="10" customFormat="1" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="16" t="str">
+        <f>"Code"&amp;":"&amp;الجدول2[[#This Row],[Code]]&amp;","&amp;CHAR(10)&amp;"Item"&amp;": "&amp;ورقة1!$B3&amp;","&amp;CHAR(10)&amp;"Model"&amp;":"&amp;الجدول2[[#This Row],[Model]]&amp;","&amp;CHAR(10)&amp;"Number"&amp;":"&amp;الجدول2[[#This Row],[Number]]&amp;","&amp;CHAR(10)&amp;"S/N &amp; VIN"&amp;":"&amp;الجدول2[[#This Row],[S/N &amp; VIN]]&amp;","&amp;CHAR(10)&amp;"Site"&amp;": "&amp;ورقة1!$F3&amp;","&amp;CHAR(10)&amp;"In custody"&amp;": "&amp;ورقة1!$G3</f>
+        <v xml:space="preserve">Code:,
+Item: ,
+Model:,
+Number:,
+S/N &amp; VIN:,
 Site: ,
 In custody: </v>
       </c>
-      <c r="E3" s="4" t="e" vm="2">
-        <f>_xlfn.IMAGE("https://quickchart.io/qr?text=" &amp; _xlfn.ENCODEURL(D3),الجدول1[[#This Row],[Item Name]],3,90,90)</f>
+      <c r="I3" s="17" t="e" vm="2">
+        <f>_xlfn.IMAGE("https://quickchart.io/qr?text=" &amp; _xlfn.ENCODEURL(H3),ورقة1!$B3,3,90,90)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="4" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="6" t="str">
-        <f>"Item"&amp;": "&amp;الجدول1[[#This Row],[Item Name]]&amp;","&amp;CHAR(10)&amp;"Site"&amp;": "&amp;الجدول1[[#This Row],[site]]&amp;","&amp;CHAR(10)&amp;"In custody"&amp;": "&amp;الجدول1[[#This Row],[In custody]]</f>
-        <v xml:space="preserve">Item: ,
+    <row r="4" spans="1:9" s="10" customFormat="1" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="16" t="str">
+        <f>"Code"&amp;":"&amp;الجدول2[[#This Row],[Code]]&amp;","&amp;CHAR(10)&amp;"Item"&amp;": "&amp;ورقة1!$B4&amp;","&amp;CHAR(10)&amp;"Model"&amp;":"&amp;الجدول2[[#This Row],[Model]]&amp;","&amp;CHAR(10)&amp;"Number"&amp;":"&amp;الجدول2[[#This Row],[Number]]&amp;","&amp;CHAR(10)&amp;"S/N &amp; VIN"&amp;":"&amp;الجدول2[[#This Row],[S/N &amp; VIN]]&amp;","&amp;CHAR(10)&amp;"Site"&amp;": "&amp;ورقة1!$F4&amp;","&amp;CHAR(10)&amp;"In custody"&amp;": "&amp;ورقة1!$G4</f>
+        <v xml:space="preserve">Code:,
+Item: ,
+Model:,
+Number:,
+S/N &amp; VIN:,
 Site: ,
 In custody: </v>
       </c>
-      <c r="E4" s="4" t="e" vm="2">
-        <f>_xlfn.IMAGE("https://quickchart.io/qr?text=" &amp; _xlfn.ENCODEURL(D4),الجدول1[[#This Row],[Item Name]],3,90,90)</f>
+      <c r="I4" s="17" t="e" vm="2">
+        <f>_xlfn.IMAGE("https://quickchart.io/qr?text=" &amp; _xlfn.ENCODEURL(H4),ورقة1!$B4,3,90,90)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="4" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="7" t="str">
-        <f>"Item"&amp;": "&amp;الجدول1[[#This Row],[Item Name]]&amp;","&amp;CHAR(10)&amp;"Site"&amp;": "&amp;الجدول1[[#This Row],[site]]&amp;","&amp;CHAR(10)&amp;"In custody"&amp;": "&amp;الجدول1[[#This Row],[In custody]]</f>
-        <v xml:space="preserve">Item: ,
+    <row r="5" spans="1:9" s="10" customFormat="1" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="16" t="str">
+        <f>"Code"&amp;":"&amp;الجدول2[[#This Row],[Code]]&amp;","&amp;CHAR(10)&amp;"Item"&amp;": "&amp;ورقة1!$B5&amp;","&amp;CHAR(10)&amp;"Model"&amp;":"&amp;الجدول2[[#This Row],[Model]]&amp;","&amp;CHAR(10)&amp;"Number"&amp;":"&amp;الجدول2[[#This Row],[Number]]&amp;","&amp;CHAR(10)&amp;"S/N &amp; VIN"&amp;":"&amp;الجدول2[[#This Row],[S/N &amp; VIN]]&amp;","&amp;CHAR(10)&amp;"Site"&amp;": "&amp;ورقة1!$F5&amp;","&amp;CHAR(10)&amp;"In custody"&amp;": "&amp;ورقة1!$G5</f>
+        <v xml:space="preserve">Code:,
+Item: ,
+Model:,
+Number:,
+S/N &amp; VIN:,
 Site: ,
 In custody: </v>
       </c>
-      <c r="E5" s="4" t="e" vm="2">
-        <f>_xlfn.IMAGE("https://quickchart.io/qr?text=" &amp; _xlfn.ENCODEURL(D5),الجدول1[[#This Row],[Item Name]],3,90,90)</f>
+      <c r="I5" s="17" t="e" vm="2">
+        <f>_xlfn.IMAGE("https://quickchart.io/qr?text=" &amp; _xlfn.ENCODEURL(H5),ورقة1!$B5,3,90,90)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="4" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6" t="str">
-        <f>"Item"&amp;": "&amp;الجدول1[[#This Row],[Item Name]]&amp;","&amp;CHAR(10)&amp;"Site"&amp;": "&amp;الجدول1[[#This Row],[site]]&amp;","&amp;CHAR(10)&amp;"In custody"&amp;": "&amp;الجدول1[[#This Row],[In custody]]</f>
-        <v xml:space="preserve">Item: ,
+    <row r="6" spans="1:9" s="10" customFormat="1" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="18" t="str">
+        <f>"Code"&amp;":"&amp;الجدول2[[#This Row],[Code]]&amp;","&amp;CHAR(10)&amp;"Item"&amp;": "&amp;ورقة1!$B6&amp;","&amp;CHAR(10)&amp;"Model"&amp;":"&amp;الجدول2[[#This Row],[Model]]&amp;","&amp;CHAR(10)&amp;"Number"&amp;":"&amp;الجدول2[[#This Row],[Number]]&amp;","&amp;CHAR(10)&amp;"S/N &amp; VIN"&amp;":"&amp;الجدول2[[#This Row],[S/N &amp; VIN]]&amp;","&amp;CHAR(10)&amp;"Site"&amp;": "&amp;ورقة1!$F6&amp;","&amp;CHAR(10)&amp;"In custody"&amp;": "&amp;ورقة1!$G6</f>
+        <v xml:space="preserve">Code:,
+Item: ,
+Model:,
+Number:,
+S/N &amp; VIN:,
 Site: ,
 In custody: </v>
       </c>
-      <c r="E6" s="4" t="e" vm="2">
-        <f>_xlfn.IMAGE("https://quickchart.io/qr?text=" &amp; _xlfn.ENCODEURL(D6),الجدول1[[#This Row],[Item Name]],3,90,90)</f>
+      <c r="I6" s="19" t="e" vm="2">
+        <f>_xlfn.IMAGE("https://quickchart.io/qr?text=" &amp; _xlfn.ENCODEURL(H6),ورقة1!$B6,3,90,90)</f>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="thv58yD5jhnbHP1Mqi77hKWaMCcQ6O1vaSMLXibqVEJGO856V4+EJ+MYNKXL50pkKBnYy1mErg9j6+5JYceJcw==" saltValue="P5bZ/e6m1CFOx7NwsjPK3A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
